--- a/UCONN_QB_ANALYSIS.xlsx
+++ b/UCONN_QB_ANALYSIS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/df64bd95354a301d/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_DD1F2D42CF52DF924CE09D2AD94627C1E1EAA24B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EC3BD74-99B0-40DB-A67B-F0F09ED55485}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_DD1F2D42CF52DF924CE09D2AD94627C1E1EAA24B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA7CCDE4-FDAD-450B-93B6-CF9C28A0AAC8}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
